--- a/output/sdsa/ai_addendum_data_check.xlsx
+++ b/output/sdsa/ai_addendum_data_check.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danpost/debt_sustainability_project/output/sdsa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C387112-4271-E14E-85D4-00BBB481B39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F84E857-2C25-234C-BB9B-92EB582F6788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-240" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{178F8C1E-13F4-E749-95A5-E9775CEAC870}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="31840" windowHeight="18880" xr2:uid="{178F8C1E-13F4-E749-95A5-E9775CEAC870}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="17">
   <si>
     <t>n.a.</t>
   </si>
@@ -82,12 +82,18 @@
   <si>
     <t>% of GDP</t>
   </si>
+  <si>
+    <t>0.5 pp productivity boost</t>
+  </si>
+  <si>
+    <t>1 pp productivity boost</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -124,6 +130,14 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -151,11 +165,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -178,10 +193,20 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{43C8BCE2-BC1B-6C47-8265-279B6A2E7FF3}"/>
+    <cellStyle name="Normal 3 2" xfId="2" xr:uid="{3AB59C42-8325-0A41-B448-3160678776B8}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -513,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D60A06-5FFB-474A-8672-33A0FA63FD17}">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.5" style="6" bestFit="1" customWidth="1"/>
@@ -565,52 +590,26 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1">
-        <v>0.98</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0.98299999999999998</v>
-      </c>
-      <c r="D2" s="1">
-        <v>1.0149999999999999</v>
-      </c>
-      <c r="E2" s="1">
-        <v>1.0580000000000001</v>
-      </c>
-      <c r="F2" s="1">
-        <v>1.105</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.129</v>
-      </c>
-      <c r="H2" s="1">
-        <v>1.1259999999999999</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.125</v>
-      </c>
-      <c r="J2" s="1">
-        <v>1.121</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="L2" s="1">
-        <v>1.1140000000000001</v>
-      </c>
-      <c r="M2" s="1">
-        <v>1.1120000000000001</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="3"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1">
         <v>0.98</v>
@@ -619,34 +618,34 @@
         <v>0.98299999999999998</v>
       </c>
       <c r="D3" s="1">
-        <v>1.115</v>
+        <v>1.0149999999999999</v>
       </c>
       <c r="E3" s="1">
-        <v>1.258</v>
+        <v>1.0580000000000001</v>
       </c>
       <c r="F3" s="1">
-        <v>1.405</v>
+        <v>1.105</v>
       </c>
       <c r="G3" s="1">
-        <v>1.5289999999999999</v>
+        <v>1.129</v>
       </c>
       <c r="H3" s="1">
-        <v>1.6259999999999999</v>
+        <v>1.1259999999999999</v>
       </c>
       <c r="I3" s="1">
-        <v>1.625</v>
+        <v>1.125</v>
       </c>
       <c r="J3" s="1">
-        <v>1.621</v>
+        <v>1.121</v>
       </c>
       <c r="K3" s="1">
-        <v>1.6160000000000001</v>
+        <v>1.1160000000000001</v>
       </c>
       <c r="L3" s="1">
-        <v>1.6140000000000001</v>
+        <v>1.1140000000000001</v>
       </c>
       <c r="M3" s="1">
-        <v>1.6120000000000001</v>
+        <v>1.1120000000000001</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>6</v>
@@ -654,424 +653,969 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.98</v>
       </c>
       <c r="C4" s="1">
-        <v>0</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="D4" s="1">
-        <v>4.6920000000000002</v>
+        <v>1.115</v>
       </c>
       <c r="E4" s="1">
-        <v>16.899000000000001</v>
+        <v>1.258</v>
       </c>
       <c r="F4" s="1">
-        <v>37.689</v>
+        <v>1.405</v>
       </c>
       <c r="G4" s="1">
-        <v>68.355000000000004</v>
+        <v>1.5289999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>110.40300000000001</v>
+        <v>1.6259999999999999</v>
       </c>
       <c r="I4" s="1">
-        <v>159.16900000000001</v>
+        <v>1.625</v>
       </c>
       <c r="J4" s="1">
-        <v>213.49799999999999</v>
+        <v>1.621</v>
       </c>
       <c r="K4" s="1">
-        <v>273.26</v>
+        <v>1.6160000000000001</v>
       </c>
       <c r="L4" s="1">
-        <v>338.73399999999998</v>
+        <v>1.6140000000000001</v>
       </c>
       <c r="M4" s="1">
-        <v>411.03800000000001</v>
+        <v>1.6120000000000001</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="1">
         <v>0</v>
       </c>
-      <c r="D5" s="5">
-        <v>1</v>
-      </c>
-      <c r="E5" s="5">
-        <v>3</v>
-      </c>
-      <c r="F5" s="5">
+      <c r="D5" s="1">
+        <v>4.6920000000000002</v>
+      </c>
+      <c r="E5" s="1">
+        <v>16.899000000000001</v>
+      </c>
+      <c r="F5" s="1">
+        <v>37.689</v>
+      </c>
+      <c r="G5" s="1">
+        <v>68.355000000000004</v>
+      </c>
+      <c r="H5" s="1">
+        <v>110.40300000000001</v>
+      </c>
+      <c r="I5" s="1">
+        <v>159.16900000000001</v>
+      </c>
+      <c r="J5" s="1">
+        <v>213.49799999999999</v>
+      </c>
+      <c r="K5" s="1">
+        <v>273.26</v>
+      </c>
+      <c r="L5" s="1">
+        <v>338.73399999999998</v>
+      </c>
+      <c r="M5" s="1">
+        <v>411.03800000000001</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="5">
-        <v>14</v>
-      </c>
-      <c r="H5" s="5">
-        <v>25</v>
-      </c>
-      <c r="I5" s="5">
-        <v>38</v>
-      </c>
-      <c r="J5" s="5">
-        <v>53</v>
-      </c>
-      <c r="K5" s="5">
-        <v>70</v>
-      </c>
-      <c r="L5" s="5">
-        <v>88</v>
-      </c>
-      <c r="M5" s="5">
-        <v>107</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="O5" s="7"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="5">
         <v>0</v>
       </c>
-      <c r="D6" s="1">
-        <v>3.831</v>
-      </c>
-      <c r="E6" s="1">
-        <v>13.07</v>
-      </c>
-      <c r="F6" s="1">
-        <v>27.82</v>
-      </c>
-      <c r="G6" s="1">
-        <v>49.501000000000005</v>
-      </c>
-      <c r="H6" s="1">
-        <v>78.004999999999995</v>
-      </c>
-      <c r="I6" s="1">
-        <v>109.77200000000001</v>
-      </c>
-      <c r="J6" s="1">
-        <v>144.11599999999999</v>
-      </c>
-      <c r="K6" s="1">
-        <v>181.72499999999999</v>
-      </c>
-      <c r="L6" s="1">
-        <v>223.16999999999996</v>
-      </c>
-      <c r="M6" s="1">
-        <v>269.58300000000003</v>
-      </c>
-      <c r="N6" s="1" t="s">
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3</v>
+      </c>
+      <c r="F6" s="5">
         <v>7</v>
       </c>
+      <c r="G6" s="5">
+        <v>14</v>
+      </c>
+      <c r="H6" s="5">
+        <v>25</v>
+      </c>
+      <c r="I6" s="5">
+        <v>38</v>
+      </c>
+      <c r="J6" s="5">
+        <v>53</v>
+      </c>
+      <c r="K6" s="5">
+        <v>70</v>
+      </c>
+      <c r="L6" s="5">
+        <v>88</v>
+      </c>
+      <c r="M6" s="5">
+        <v>107</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="O6" s="7"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3.831</v>
+      </c>
+      <c r="E7" s="1">
+        <v>13.07</v>
+      </c>
+      <c r="F7" s="1">
+        <v>27.82</v>
+      </c>
+      <c r="G7" s="1">
+        <v>49.501000000000005</v>
+      </c>
+      <c r="H7" s="1">
+        <v>78.004999999999995</v>
+      </c>
+      <c r="I7" s="1">
+        <v>109.77200000000001</v>
+      </c>
+      <c r="J7" s="1">
+        <v>144.11599999999999</v>
+      </c>
+      <c r="K7" s="1">
+        <v>181.72499999999999</v>
+      </c>
+      <c r="L7" s="1">
+        <v>223.16999999999996</v>
+      </c>
+      <c r="M7" s="1">
+        <v>269.58300000000003</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1">
-        <f>(-1*C6)-C5</f>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1">
+        <f>(-1*C7)-C6</f>
         <v>0</v>
       </c>
-      <c r="D7" s="1">
-        <f t="shared" ref="D7:M7" si="0">(-1*D6)-D5</f>
+      <c r="D8" s="1">
+        <f t="shared" ref="D8:M8" si="0">(-1*D7)-D6</f>
         <v>-4.8309999999999995</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E8" s="1">
         <f t="shared" si="0"/>
         <v>-16.07</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F8" s="1">
         <f t="shared" si="0"/>
         <v>-34.82</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G8" s="1">
         <f t="shared" si="0"/>
         <v>-63.501000000000005</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H8" s="1">
         <f t="shared" si="0"/>
         <v>-103.005</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I8" s="1">
         <f t="shared" si="0"/>
         <v>-147.77199999999999</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J8" s="1">
         <f t="shared" si="0"/>
         <v>-197.11599999999999</v>
       </c>
-      <c r="K7" s="1">
+      <c r="K8" s="1">
         <f t="shared" si="0"/>
         <v>-251.72499999999999</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L8" s="1">
         <f t="shared" si="0"/>
         <v>-311.16999999999996</v>
       </c>
-      <c r="M7" s="1">
+      <c r="M8" s="1">
         <f t="shared" si="0"/>
         <v>-376.58300000000003</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="N8" s="1" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="6">
-        <v>2.734</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2.125</v>
-      </c>
-      <c r="D8" s="6">
-        <v>1.9379999999999999</v>
-      </c>
-      <c r="E8" s="6">
-        <v>1.988</v>
-      </c>
-      <c r="F8" s="6">
-        <v>2.0880000000000001</v>
-      </c>
-      <c r="G8" s="6">
-        <v>2.25</v>
-      </c>
-      <c r="H8" s="6">
-        <v>2.411</v>
-      </c>
-      <c r="I8" s="6">
-        <v>2.4289999999999998</v>
-      </c>
-      <c r="J8" s="6">
-        <v>2.4660000000000002</v>
-      </c>
-      <c r="K8" s="6">
-        <v>2.4660000000000002</v>
-      </c>
-      <c r="L8" s="6">
-        <v>2.4510000000000001</v>
-      </c>
-      <c r="M8" s="6">
-        <v>2.4279999999999999</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="6">
+        <v>2.734</v>
+      </c>
+      <c r="C9" s="6">
+        <v>2.125</v>
+      </c>
+      <c r="D9" s="6">
+        <v>1.9379999999999999</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1.988</v>
+      </c>
+      <c r="F9" s="6">
+        <v>2.0880000000000001</v>
+      </c>
+      <c r="G9" s="6">
+        <v>2.25</v>
+      </c>
+      <c r="H9" s="6">
+        <v>2.411</v>
+      </c>
+      <c r="I9" s="6">
+        <v>2.4289999999999998</v>
+      </c>
+      <c r="J9" s="6">
+        <v>2.4660000000000002</v>
+      </c>
+      <c r="K9" s="6">
+        <v>2.4660000000000002</v>
+      </c>
+      <c r="L9" s="6">
+        <v>2.4510000000000001</v>
+      </c>
+      <c r="M9" s="6">
+        <v>2.4279999999999999</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B10" s="6">
         <v>23290.9</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C10" s="6">
         <v>23785.8</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D10" s="6">
         <v>24246.799999999999</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E10" s="6">
         <v>24728.799999999999</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F10" s="6">
         <v>25245.1</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G10" s="6">
         <v>25813.1</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H10" s="6">
         <v>26435.5</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I10" s="6">
         <v>27077.5</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J10" s="6">
         <v>27745.200000000001</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K10" s="6">
         <v>28429.3</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L10" s="6">
         <v>29126.2</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M10" s="6">
         <v>29833.3</v>
       </c>
-      <c r="N9" s="6" t="s">
+      <c r="N10" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="6">
-        <f>(B7/B9) * 100</f>
+      <c r="B11" s="6">
+        <f>(B8/B10) * 100</f>
         <v>0</v>
       </c>
-      <c r="C10" s="6">
-        <f t="shared" ref="C10:M10" si="1">(C7/C9) * 100</f>
+      <c r="C11" s="6">
+        <f t="shared" ref="C11:M11" si="1">(C8/C10) * 100</f>
         <v>0</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D11" s="6">
         <f t="shared" si="1"/>
         <v>-1.9924278667700478E-2</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E11" s="6">
         <f t="shared" si="1"/>
         <v>-6.4984956811491051E-2</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F11" s="6">
         <f t="shared" si="1"/>
         <v>-0.13792775627745582</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G11" s="6">
         <f t="shared" si="1"/>
         <v>-0.24600299847751728</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H11" s="6">
         <f t="shared" si="1"/>
         <v>-0.38964649808023299</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I11" s="6">
         <f t="shared" si="1"/>
         <v>-0.54573723571230726</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J11" s="6">
         <f t="shared" si="1"/>
         <v>-0.7104508167178466</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K11" s="6">
         <f t="shared" si="1"/>
         <v>-0.88544213188506227</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L11" s="6">
         <f t="shared" si="1"/>
         <v>-1.0683508318970547</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M11" s="6">
         <f t="shared" si="1"/>
         <v>-1.262290795855638</v>
       </c>
-      <c r="N10" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="6">
-        <v>3</v>
-      </c>
-      <c r="D12" s="6">
-        <v>3.8</v>
-      </c>
-      <c r="E12" s="6">
-        <v>3.6</v>
-      </c>
-      <c r="F12" s="6">
-        <v>3.3</v>
-      </c>
-      <c r="G12" s="6">
-        <v>3.6</v>
-      </c>
-      <c r="H12" s="6">
-        <v>3.3</v>
-      </c>
-      <c r="I12" s="6">
-        <v>3.1</v>
-      </c>
-      <c r="J12" s="6">
-        <v>3</v>
-      </c>
-      <c r="K12" s="6">
-        <v>2.9</v>
-      </c>
-      <c r="L12" s="6">
-        <v>3</v>
-      </c>
-      <c r="M12" s="6">
-        <v>2.9</v>
-      </c>
-      <c r="N12" s="6" t="s">
+      <c r="N11" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="6">
+        <v>3</v>
+      </c>
+      <c r="D13" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="E13" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="F13" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="G13" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="H13" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="I13" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="J13" s="6">
+        <v>3</v>
+      </c>
+      <c r="K13" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="L13" s="6">
+        <v>3</v>
+      </c>
+      <c r="M13" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="6">
-        <f>B12+B10</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="6">
-        <f>D12+D10</f>
+      <c r="C14" s="6">
+        <f>C13+C11</f>
+        <v>3</v>
+      </c>
+      <c r="D14" s="6">
+        <f>D13+D11</f>
         <v>3.7800757213322993</v>
       </c>
-      <c r="E13" s="6">
-        <f t="shared" ref="E13:M13" si="2">E12+E10</f>
+      <c r="E14" s="6">
+        <f t="shared" ref="E14:M14" si="2">E13+E11</f>
         <v>3.5350150431885092</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F14" s="6">
         <f t="shared" si="2"/>
         <v>3.1620722437225441</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G14" s="6">
         <f t="shared" si="2"/>
         <v>3.3539970015224827</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H14" s="6">
         <f t="shared" si="2"/>
         <v>2.9103535019197668</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I14" s="6">
         <f t="shared" si="2"/>
         <v>2.5542627642876927</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J14" s="6">
         <f t="shared" si="2"/>
         <v>2.2895491832821535</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K14" s="6">
         <f t="shared" si="2"/>
         <v>2.0145578681149376</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L14" s="6">
         <f t="shared" si="2"/>
         <v>1.9316491681029453</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M14" s="6">
         <f t="shared" si="2"/>
         <v>1.6377092041443619</v>
       </c>
-      <c r="N13" s="6" t="s">
+      <c r="N14" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="6">
+        <v>0.98</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="D17" s="6">
+        <v>1.0149999999999999</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1.0580000000000001</v>
+      </c>
+      <c r="F17" s="6">
+        <v>1.105</v>
+      </c>
+      <c r="G17" s="6">
+        <v>1.129</v>
+      </c>
+      <c r="H17" s="6">
+        <v>1.1259999999999999</v>
+      </c>
+      <c r="I17" s="6">
+        <v>1.125</v>
+      </c>
+      <c r="J17" s="6">
+        <v>1.121</v>
+      </c>
+      <c r="K17" s="6">
+        <v>1.1160000000000001</v>
+      </c>
+      <c r="L17" s="6">
+        <v>1.1140000000000001</v>
+      </c>
+      <c r="M17" s="6">
+        <v>1.1120000000000001</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="6">
+        <v>0.98</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="D18" s="6">
+        <v>2.0149999999999997</v>
+      </c>
+      <c r="E18" s="6">
+        <v>2.0579999999999998</v>
+      </c>
+      <c r="F18" s="6">
+        <v>2.105</v>
+      </c>
+      <c r="G18" s="6">
+        <v>2.129</v>
+      </c>
+      <c r="H18" s="6">
+        <v>2.1259999999999999</v>
+      </c>
+      <c r="I18" s="6">
+        <v>2.125</v>
+      </c>
+      <c r="J18" s="6">
+        <v>2.121</v>
+      </c>
+      <c r="K18" s="6">
+        <v>2.1160000000000001</v>
+      </c>
+      <c r="L18" s="6">
+        <v>2.1139999999999999</v>
+      </c>
+      <c r="M18" s="6">
+        <v>2.1120000000000001</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0</v>
+      </c>
+      <c r="D19" s="6">
+        <v>46.814999999999998</v>
+      </c>
+      <c r="E19" s="6">
+        <v>119.047</v>
+      </c>
+      <c r="F19" s="6">
+        <v>200.55099999999999</v>
+      </c>
+      <c r="G19" s="6">
+        <v>291.88099999999997</v>
+      </c>
+      <c r="H19" s="6">
+        <v>393.90800000000002</v>
+      </c>
+      <c r="I19" s="6">
+        <v>506.81099999999998</v>
+      </c>
+      <c r="J19" s="6">
+        <v>632.23400000000004</v>
+      </c>
+      <c r="K19" s="6">
+        <v>769.66800000000001</v>
+      </c>
+      <c r="L19" s="6">
+        <v>919.68899999999996</v>
+      </c>
+      <c r="M19" s="6">
+        <v>1085.5409999999999</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6">
+        <v>6.7829999999999995</v>
+      </c>
+      <c r="E20" s="6">
+        <v>21.690999999999999</v>
+      </c>
+      <c r="F20" s="6">
+        <v>41.524000000000001</v>
+      </c>
+      <c r="G20" s="6">
+        <v>65.338999999999999</v>
+      </c>
+      <c r="H20" s="6">
+        <v>93.185999999999993</v>
+      </c>
+      <c r="I20" s="6">
+        <v>124.35999999999999</v>
+      </c>
+      <c r="J20" s="6">
+        <v>158.29200000000003</v>
+      </c>
+      <c r="K20" s="6">
+        <v>192.572</v>
+      </c>
+      <c r="L20" s="6">
+        <v>228.57799999999997</v>
+      </c>
+      <c r="M20" s="6">
+        <v>264.07399999999996</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0</v>
+      </c>
+      <c r="D21" s="6">
+        <v>37.970999999999997</v>
+      </c>
+      <c r="E21" s="6">
+        <v>90.670999999999992</v>
+      </c>
+      <c r="F21" s="6">
+        <v>145.16799999999998</v>
+      </c>
+      <c r="G21" s="6">
+        <v>206.98999999999998</v>
+      </c>
+      <c r="H21" s="6">
+        <v>273.20500000000004</v>
+      </c>
+      <c r="I21" s="6">
+        <v>346.01299999999998</v>
+      </c>
+      <c r="J21" s="6">
+        <v>426.71100000000001</v>
+      </c>
+      <c r="K21" s="6">
+        <v>516.49099999999999</v>
+      </c>
+      <c r="L21" s="6">
+        <v>616.90699999999993</v>
+      </c>
+      <c r="M21" s="6">
+        <v>730.572</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="6">
+        <f>(-1*D21)-D20</f>
+        <v>-44.753999999999998</v>
+      </c>
+      <c r="E22" s="6">
+        <f t="shared" ref="E22:M22" si="3">(-1*E21)-E20</f>
+        <v>-112.36199999999999</v>
+      </c>
+      <c r="F22" s="6">
+        <f t="shared" si="3"/>
+        <v>-186.69199999999998</v>
+      </c>
+      <c r="G22" s="6">
+        <f t="shared" si="3"/>
+        <v>-272.32899999999995</v>
+      </c>
+      <c r="H22" s="6">
+        <f t="shared" si="3"/>
+        <v>-366.39100000000002</v>
+      </c>
+      <c r="I22" s="6">
+        <f t="shared" si="3"/>
+        <v>-470.37299999999993</v>
+      </c>
+      <c r="J22" s="6">
+        <f t="shared" si="3"/>
+        <v>-585.00300000000004</v>
+      </c>
+      <c r="K22" s="6">
+        <f t="shared" si="3"/>
+        <v>-709.06299999999999</v>
+      </c>
+      <c r="L22" s="6">
+        <f t="shared" si="3"/>
+        <v>-845.4849999999999</v>
+      </c>
+      <c r="M22" s="6">
+        <f t="shared" si="3"/>
+        <v>-994.64599999999996</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="6">
+        <v>2.734</v>
+      </c>
+      <c r="C23" s="6">
+        <v>2.125</v>
+      </c>
+      <c r="D23" s="6">
+        <v>2.9319999999999999</v>
+      </c>
+      <c r="E23" s="6">
+        <v>2.9060000000000001</v>
+      </c>
+      <c r="F23" s="6">
+        <v>2.923</v>
+      </c>
+      <c r="G23" s="6">
+        <v>2.9969999999999999</v>
+      </c>
+      <c r="H23" s="6">
+        <v>3.0640000000000001</v>
+      </c>
+      <c r="I23" s="6">
+        <v>3.093</v>
+      </c>
+      <c r="J23" s="6">
+        <v>3.141</v>
+      </c>
+      <c r="K23" s="6">
+        <v>3.15</v>
+      </c>
+      <c r="L23" s="6">
+        <v>3.145</v>
+      </c>
+      <c r="M23" s="6">
+        <v>3.1309999999999998</v>
+      </c>
+      <c r="N23" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="6">
+        <v>23290.9</v>
+      </c>
+      <c r="C24" s="6">
+        <v>23785.8</v>
+      </c>
+      <c r="D24" s="6">
+        <v>24483.200000000001</v>
+      </c>
+      <c r="E24" s="6">
+        <v>25194.7</v>
+      </c>
+      <c r="F24" s="6">
+        <v>25931.1</v>
+      </c>
+      <c r="G24" s="6">
+        <v>26708.2</v>
+      </c>
+      <c r="H24" s="6">
+        <v>27526.5</v>
+      </c>
+      <c r="I24" s="6">
+        <v>28377.8</v>
+      </c>
+      <c r="J24" s="6">
+        <v>29269.1</v>
+      </c>
+      <c r="K24" s="6">
+        <v>30191.200000000001</v>
+      </c>
+      <c r="L24" s="6">
+        <v>31140.7</v>
+      </c>
+      <c r="M24" s="6">
+        <v>32115.599999999999</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="6">
+        <f xml:space="preserve"> (B21 / B24) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="6">
+        <f t="shared" ref="C25:M25" si="4" xml:space="preserve"> (C21 / C24) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="6">
+        <f xml:space="preserve"> (D22 / D24) * 100</f>
+        <v>-0.1827947327146778</v>
+      </c>
+      <c r="E25" s="6">
+        <f t="shared" ref="E25:M25" si="5" xml:space="preserve"> (E22 / E24) * 100</f>
+        <v>-0.44597474865745568</v>
+      </c>
+      <c r="F25" s="6">
+        <f t="shared" si="5"/>
+        <v>-0.71995403203103603</v>
+      </c>
+      <c r="G25" s="6">
+        <f t="shared" si="5"/>
+        <v>-1.0196456518971699</v>
+      </c>
+      <c r="H25" s="6">
+        <f t="shared" si="5"/>
+        <v>-1.3310482625833289</v>
+      </c>
+      <c r="I25" s="6">
+        <f t="shared" si="5"/>
+        <v>-1.6575386393589353</v>
+      </c>
+      <c r="J25" s="6">
+        <f t="shared" si="5"/>
+        <v>-1.9987051190504663</v>
+      </c>
+      <c r="K25" s="6">
+        <f t="shared" si="5"/>
+        <v>-2.3485750814806963</v>
+      </c>
+      <c r="L25" s="6">
+        <f t="shared" si="5"/>
+        <v>-2.7150481524178964</v>
+      </c>
+      <c r="M25" s="6">
+        <f t="shared" si="5"/>
+        <v>-3.0970805465256759</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="6">
+        <v>3</v>
+      </c>
+      <c r="D27" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="E27" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="F27" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="G27" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="H27" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="I27" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="J27" s="6">
+        <v>3</v>
+      </c>
+      <c r="K27" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="L27" s="6">
+        <v>3</v>
+      </c>
+      <c r="M27" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="N27" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="6">
+        <f>C27+C25</f>
+        <v>3</v>
+      </c>
+      <c r="D28" s="6">
+        <f t="shared" ref="D28:M28" si="6">D27+D25</f>
+        <v>3.6172052672853221</v>
+      </c>
+      <c r="E28" s="6">
+        <f t="shared" si="6"/>
+        <v>3.1540252513425444</v>
+      </c>
+      <c r="F28" s="6">
+        <f t="shared" si="6"/>
+        <v>2.5800459679689638</v>
+      </c>
+      <c r="G28" s="6">
+        <f t="shared" si="6"/>
+        <v>2.5803543481028299</v>
+      </c>
+      <c r="H28" s="6">
+        <f t="shared" si="6"/>
+        <v>1.968951737416671</v>
+      </c>
+      <c r="I28" s="6">
+        <f t="shared" si="6"/>
+        <v>1.4424613606410648</v>
+      </c>
+      <c r="J28" s="6">
+        <f t="shared" si="6"/>
+        <v>1.0012948809495337</v>
+      </c>
+      <c r="K28" s="6">
+        <f t="shared" si="6"/>
+        <v>0.55142491851930364</v>
+      </c>
+      <c r="L28" s="6">
+        <f t="shared" si="6"/>
+        <v>0.28495184758210357</v>
+      </c>
+      <c r="M28" s="6">
+        <f t="shared" si="6"/>
+        <v>-0.19708054652567597</v>
+      </c>
+      <c r="N28" s="6" t="s">
         <v>14</v>
       </c>
     </row>
